--- a/Analysis/Hybrid_Ablation/hybrid_ablation_posthoc_tests.xlsx
+++ b/Analysis/Hybrid_Ablation/hybrid_ablation_posthoc_tests.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K28"/>
+  <dimension ref="A1:K37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -881,7 +881,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -906,7 +906,7 @@
         <v>8.291792926723148e-13</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.3298969072164948</v>
+        <v>-0.3282051282051282</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="J11" t="n">
         <v>2.487537878016945e-12</v>
@@ -926,7 +926,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -945,13 +945,13 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>126</v>
+        <v>309</v>
       </c>
       <c r="F12" t="n">
-        <v>2.441181074772002e-09</v>
+        <v>6.071753852119681e-08</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.2341640982038474</v>
+        <v>-0.2392110453648915</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -959,10 +959,10 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="J12" t="n">
-        <v>4.882362149544004e-09</v>
+        <v>1.214350770423936e-07</v>
       </c>
       <c r="K12" t="b">
         <v>1</v>
@@ -971,7 +971,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -993,10 +993,10 @@
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>7.097908330908269e-06</v>
+        <v>3.833012152637274e-05</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.1082474226804124</v>
+        <v>-0.09743589743589744</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -1004,10 +1004,10 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="J13" t="n">
-        <v>7.097908330908269e-06</v>
+        <v>3.833012152637274e-05</v>
       </c>
       <c r="K13" t="b">
         <v>1</v>
@@ -1016,7 +1016,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1041,7 +1041,7 @@
         <v>1.970344471179917e-11</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.2319587628865979</v>
+        <v>-0.2307692307692308</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1049,7 +1049,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="J14" t="n">
         <v>5.91103341353975e-11</v>
@@ -1061,7 +1061,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1080,13 +1080,13 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>141</v>
+        <v>297</v>
       </c>
       <c r="F15" t="n">
-        <v>5.358051166961492e-07</v>
+        <v>2.061002941256615e-05</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.1752577319587629</v>
+        <v>-0.158974358974359</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -1094,10 +1094,10 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="J15" t="n">
-        <v>1.071610233392298e-06</v>
+        <v>4.12200588251323e-05</v>
       </c>
       <c r="K15" t="b">
         <v>1</v>
@@ -1106,7 +1106,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1128,10 +1128,10 @@
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0009111188771537128</v>
+        <v>0.0001828106329818348</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.05670103092783505</v>
+        <v>-0.07179487179487179</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="J16" t="n">
-        <v>0.0009111188771537128</v>
+        <v>0.0001828106329818348</v>
       </c>
       <c r="K16" t="b">
         <v>1</v>
@@ -1151,7 +1151,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>extracted</t>
+          <t>default_params</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1173,10 +1173,10 @@
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>4.130764843359505e-32</v>
+        <v>1.873961246940136e-31</v>
       </c>
       <c r="G17" t="n">
-        <v>0.9536082474226805</v>
+        <v>0.9282051282051282</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1184,10 +1184,10 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="J17" t="n">
-        <v>1.239229453007851e-31</v>
+        <v>5.621883740820408e-31</v>
       </c>
       <c r="K17" t="b">
         <v>1</v>
@@ -1196,7 +1196,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1206,7 +1206,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>default_params</t>
+          <t>extracted</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1218,10 +1218,10 @@
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>2.734031108421746e-31</v>
+        <v>1.806028382396314e-30</v>
       </c>
       <c r="G18" t="n">
-        <v>0.9278350515463918</v>
+        <v>0.8974358974358975</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -1229,10 +1229,10 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="J18" t="n">
-        <v>5.468062216843493e-31</v>
+        <v>3.612056764792628e-30</v>
       </c>
       <c r="K18" t="b">
         <v>1</v>
@@ -1241,7 +1241,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1260,13 +1260,13 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1457</v>
+        <v>1190.5</v>
       </c>
       <c r="F19" t="n">
-        <v>1.250985422608859e-21</v>
+        <v>2.335491017221078e-19</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4412530555850781</v>
+        <v>0.4536752136752137</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -1274,10 +1274,10 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="J19" t="n">
-        <v>1.250985422608859e-21</v>
+        <v>2.335491017221078e-19</v>
       </c>
       <c r="K19" t="b">
         <v>1</v>
@@ -1286,7 +1286,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>qwen</t>
+          <t>gptoss</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1311,7 +1311,7 @@
         <v>8.291792926723148e-13</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.3282051282051282</v>
+        <v>-0.3298969072164948</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="J20" t="n">
         <v>2.487537878016945e-12</v>
@@ -1331,7 +1331,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>qwen</t>
+          <t>gptoss</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1350,13 +1350,13 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>231</v>
+        <v>126</v>
       </c>
       <c r="F21" t="n">
-        <v>2.586741349189714e-07</v>
+        <v>2.441181074772002e-09</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.218172255095332</v>
+        <v>-0.2341640982038474</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -1364,10 +1364,10 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="J21" t="n">
-        <v>5.173482698379428e-07</v>
+        <v>4.882362149544004e-09</v>
       </c>
       <c r="K21" t="b">
         <v>1</v>
@@ -1376,7 +1376,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>qwen</t>
+          <t>gptoss</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1398,10 +1398,10 @@
         <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>8.363093641038174e-06</v>
+        <v>7.097908330908269e-06</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.1179487179487179</v>
+        <v>-0.1082474226804124</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -1409,10 +1409,10 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="J22" t="n">
-        <v>8.363093641038174e-06</v>
+        <v>7.097908330908269e-06</v>
       </c>
       <c r="K22" t="b">
         <v>1</v>
@@ -1421,7 +1421,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>qwen</t>
+          <t>gptoss</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1446,7 +1446,7 @@
         <v>1.970344471179917e-11</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.2307692307692308</v>
+        <v>-0.2319587628865979</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="J23" t="n">
         <v>5.91103341353975e-11</v>
@@ -1466,7 +1466,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>qwen</t>
+          <t>gptoss</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1485,24 +1485,24 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>180</v>
+        <v>141</v>
       </c>
       <c r="F24" t="n">
-        <v>2.430496069477897e-05</v>
+        <v>5.358051166961492e-07</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.1435897435897436</v>
+        <v>-0.1752577319587629</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>negligible</t>
+          <t>small</t>
         </is>
       </c>
       <c r="I24" t="n">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="J24" t="n">
-        <v>4.860992138955793e-05</v>
+        <v>1.071610233392298e-06</v>
       </c>
       <c r="K24" t="b">
         <v>1</v>
@@ -1511,7 +1511,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>qwen</t>
+          <t>gptoss</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1533,10 +1533,10 @@
         <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>3.737981840170154e-05</v>
+        <v>0.0009111188771537128</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.08717948717948718</v>
+        <v>-0.05670103092783505</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
@@ -1544,10 +1544,10 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="J25" t="n">
-        <v>3.737981840170154e-05</v>
+        <v>0.0009111188771537128</v>
       </c>
       <c r="K25" t="b">
         <v>1</v>
@@ -1556,7 +1556,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>qwen</t>
+          <t>gptoss</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1566,7 +1566,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>default_params</t>
+          <t>extracted</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1578,10 +1578,10 @@
         <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>1.873961246940136e-31</v>
+        <v>4.130764843359505e-32</v>
       </c>
       <c r="G26" t="n">
-        <v>0.9282051282051282</v>
+        <v>0.9536082474226805</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -1589,10 +1589,10 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="J26" t="n">
-        <v>5.621883740820408e-31</v>
+        <v>1.239229453007851e-31</v>
       </c>
       <c r="K26" t="b">
         <v>1</v>
@@ -1601,7 +1601,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>qwen</t>
+          <t>gptoss</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>extracted</t>
+          <t>default_params</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1623,10 +1623,10 @@
         <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>3.847966508546606e-30</v>
+        <v>2.734031108421746e-31</v>
       </c>
       <c r="G27" t="n">
-        <v>0.8871794871794871</v>
+        <v>0.9278350515463918</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
@@ -1634,10 +1634,10 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="J27" t="n">
-        <v>7.695933017093212e-30</v>
+        <v>5.468062216843493e-31</v>
       </c>
       <c r="K27" t="b">
         <v>1</v>
@@ -1646,45 +1646,450 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>gptoss</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>mae</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>default_params</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>1457</v>
+      </c>
+      <c r="F28" t="n">
+        <v>1.250985422608859e-21</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0.4412530555850781</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
+        <v>194</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1.250985422608859e-21</v>
+      </c>
+      <c r="K28" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
           <t>qwen</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>kendall_tau</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>default_params</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>true_params</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" t="n">
+        <v>8.291792926723148e-13</v>
+      </c>
+      <c r="G29" t="n">
+        <v>-0.3282051282051282</v>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>small</t>
+        </is>
+      </c>
+      <c r="I29" t="n">
+        <v>195</v>
+      </c>
+      <c r="J29" t="n">
+        <v>2.487537878016945e-12</v>
+      </c>
+      <c r="K29" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>qwen</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>kendall_tau</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>default_params</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>231</v>
+      </c>
+      <c r="F30" t="n">
+        <v>2.586741349189714e-07</v>
+      </c>
+      <c r="G30" t="n">
+        <v>-0.218172255095332</v>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>small</t>
+        </is>
+      </c>
+      <c r="I30" t="n">
+        <v>195</v>
+      </c>
+      <c r="J30" t="n">
+        <v>5.173482698379428e-07</v>
+      </c>
+      <c r="K30" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>qwen</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>kendall_tau</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>true_params</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" t="n">
+        <v>8.363093641038174e-06</v>
+      </c>
+      <c r="G31" t="n">
+        <v>-0.1179487179487179</v>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>negligible</t>
+        </is>
+      </c>
+      <c r="I31" t="n">
+        <v>195</v>
+      </c>
+      <c r="J31" t="n">
+        <v>8.363093641038174e-06</v>
+      </c>
+      <c r="K31" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>qwen</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>top1</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>default_params</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>true_params</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" t="n">
+        <v>1.970344471179917e-11</v>
+      </c>
+      <c r="G32" t="n">
+        <v>-0.2307692307692308</v>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>small</t>
+        </is>
+      </c>
+      <c r="I32" t="n">
+        <v>195</v>
+      </c>
+      <c r="J32" t="n">
+        <v>5.91103341353975e-11</v>
+      </c>
+      <c r="K32" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>qwen</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>top1</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>default_params</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>180</v>
+      </c>
+      <c r="F33" t="n">
+        <v>2.430496069477897e-05</v>
+      </c>
+      <c r="G33" t="n">
+        <v>-0.1435897435897436</v>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>negligible</t>
+        </is>
+      </c>
+      <c r="I33" t="n">
+        <v>195</v>
+      </c>
+      <c r="J33" t="n">
+        <v>4.860992138955793e-05</v>
+      </c>
+      <c r="K33" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>qwen</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>top1</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>true_params</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" t="n">
+        <v>3.737981840170154e-05</v>
+      </c>
+      <c r="G34" t="n">
+        <v>-0.08717948717948718</v>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>negligible</t>
+        </is>
+      </c>
+      <c r="I34" t="n">
+        <v>195</v>
+      </c>
+      <c r="J34" t="n">
+        <v>3.737981840170154e-05</v>
+      </c>
+      <c r="K34" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>qwen</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
         <is>
           <t>mae</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>default_params</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>extracted</t>
-        </is>
-      </c>
-      <c r="E28" t="n">
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>default_params</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>true_params</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" t="n">
+        <v>1.873961246940136e-31</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0.9282051282051282</v>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>large</t>
+        </is>
+      </c>
+      <c r="I35" t="n">
+        <v>195</v>
+      </c>
+      <c r="J35" t="n">
+        <v>5.621883740820408e-31</v>
+      </c>
+      <c r="K35" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>qwen</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>mae</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>true_params</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" t="n">
+        <v>3.847966508546606e-30</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0.8871794871794871</v>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>large</t>
+        </is>
+      </c>
+      <c r="I36" t="n">
+        <v>195</v>
+      </c>
+      <c r="J36" t="n">
+        <v>7.695933017093212e-30</v>
+      </c>
+      <c r="K36" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>qwen</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>mae</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>default_params</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
         <v>3117.5</v>
       </c>
-      <c r="F28" t="n">
+      <c r="F37" t="n">
         <v>3.906073614439517e-11</v>
       </c>
-      <c r="G28" t="n">
+      <c r="G37" t="n">
         <v>0.3491913214990138</v>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="H37" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="I28" t="n">
-        <v>195</v>
-      </c>
-      <c r="J28" t="n">
+      <c r="I37" t="n">
+        <v>195</v>
+      </c>
+      <c r="J37" t="n">
         <v>3.906073614439517e-11</v>
       </c>
-      <c r="K28" t="b">
+      <c r="K37" t="b">
         <v>1</v>
       </c>
     </row>
